--- a/data/trans_orig/P04D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>40025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>44594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74391</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450893</t>
+          <t>452609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501986</t>
+          <t>501925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446461</t>
+          <t>448131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497448</t>
+          <t>498821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>914435</t>
+          <t>916399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>985286</t>
+          <t>988973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173914</t>
+          <t>173217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>222344</t>
+          <t>221445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170746</t>
+          <t>168809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218688</t>
+          <t>217224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>358263</t>
+          <t>355411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>426114</t>
+          <t>425357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81743</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634930</t>
+          <t>639185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>699743</t>
+          <t>701467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669413</t>
+          <t>666146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>728706</t>
+          <t>728452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1325788</t>
+          <t>1326679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1416606</t>
+          <t>1416534</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>288394</t>
+          <t>289341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>350220</t>
+          <t>349678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>270602</t>
+          <t>272245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>329041</t>
+          <t>333427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572576</t>
+          <t>574939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>660837</t>
+          <t>660940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40953</t>
+          <t>42890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72877</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77988</t>
+          <t>79583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120625</t>
+          <t>121333</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>478998</t>
+          <t>475605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>534067</t>
+          <t>532016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>531406</t>
+          <t>533370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>584545</t>
+          <t>584425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020478</t>
+          <t>1029098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1098774</t>
+          <t>1105108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171065</t>
+          <t>169126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224007</t>
+          <t>222923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152674</t>
+          <t>153548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>200012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336237</t>
+          <t>336216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408705</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42926</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72774</t>
+          <t>71555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>100089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468641</t>
+          <t>472018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>533965</t>
+          <t>532639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531042</t>
+          <t>529058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>594130</t>
+          <t>593701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1017746</t>
+          <t>1022097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1113125</t>
+          <t>1114923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>385333</t>
+          <t>388944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>451301</t>
+          <t>450523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>404059</t>
+          <t>404530</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>468774</t>
+          <t>469477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>803250</t>
+          <t>804511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>897109</t>
+          <t>895496</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120094</t>
+          <t>118571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>167116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186311</t>
+          <t>187873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341272</t>
+          <t>337458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2098435</t>
+          <t>2100521</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2215012</t>
+          <t>2219218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2233409</t>
+          <t>2238353</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2351145</t>
+          <t>2357039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4361926</t>
+          <t>4364789</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4531813</t>
+          <t>4534816</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1070530</t>
+          <t>1072620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1186341</t>
+          <t>1184169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1046238</t>
+          <t>1045111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1158167</t>
+          <t>1160957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2152638</t>
+          <t>2142505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2315069</t>
+          <t>2305997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105063</t>
+          <t>103879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146474</t>
+          <t>145631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95955</t>
+          <t>96742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135577</t>
+          <t>134848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213544</t>
+          <t>211457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>338246</t>
+          <t>338898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390302</t>
+          <t>390805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>347140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398816</t>
+          <t>398056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>701804</t>
+          <t>700996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775135</t>
+          <t>772927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163247</t>
+          <t>161347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209445</t>
+          <t>208867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>162147</t>
+          <t>161435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210058</t>
+          <t>205810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>335281</t>
+          <t>337334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>398833</t>
+          <t>403957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128888</t>
+          <t>128412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>176575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122204</t>
+          <t>121947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169400</t>
+          <t>167439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>261868</t>
+          <t>263652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329682</t>
+          <t>329692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>546201</t>
+          <t>545889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>613932</t>
+          <t>612094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>554369</t>
+          <t>556906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>624897</t>
+          <t>626611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1121449</t>
+          <t>1119622</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1214777</t>
+          <t>1216867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263582</t>
+          <t>262351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>322716</t>
+          <t>323775</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278393</t>
+          <t>280837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>340036</t>
+          <t>340356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557022</t>
+          <t>560203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>643463</t>
+          <t>648375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131828</t>
+          <t>134562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178358</t>
+          <t>181188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130625</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176093</t>
+          <t>179656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>277090</t>
+          <t>276711</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341021</t>
+          <t>347597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>295562</t>
+          <t>298297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>351872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291807</t>
+          <t>293719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349510</t>
+          <t>350233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606644</t>
+          <t>608545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>689301</t>
+          <t>692895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249117</t>
+          <t>249675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305241</t>
+          <t>305184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282877</t>
+          <t>284533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>341092</t>
+          <t>341422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>551899</t>
+          <t>546804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>629204</t>
+          <t>628439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81708</t>
+          <t>82254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120507</t>
+          <t>122508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83706</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124148</t>
+          <t>123730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176593</t>
+          <t>178325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232479</t>
+          <t>235450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495124</t>
+          <t>496965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556887</t>
+          <t>556478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529576</t>
+          <t>527398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>599212</t>
+          <t>597560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1047532</t>
+          <t>1043821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1137298</t>
+          <t>1137982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>279493</t>
+          <t>282271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>336067</t>
+          <t>339902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345919</t>
+          <t>343681</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>410308</t>
+          <t>411128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>640628</t>
+          <t>638202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>729609</t>
+          <t>729393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1732432</t>
+          <t>1738456</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1852822</t>
+          <t>1856736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1789213</t>
+          <t>1781384</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1905217</t>
+          <t>1905651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3557527</t>
+          <t>3560251</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3718251</t>
+          <t>3726090</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1006469</t>
+          <t>1013439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1119401</t>
+          <t>1120759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1124450</t>
+          <t>1124295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1241712</t>
+          <t>1239099</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2164138</t>
+          <t>2170944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2329712</t>
+          <t>2326782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47106</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74029</t>
+          <t>75089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444910</t>
+          <t>448394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498596</t>
+          <t>499366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>514382</t>
+          <t>516730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575903</t>
+          <t>578071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>982146</t>
+          <t>976946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1064269</t>
+          <t>1056738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113020</t>
+          <t>112619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164190</t>
+          <t>165460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118931</t>
+          <t>119550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171731</t>
+          <t>170174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>244052</t>
+          <t>249660</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>316024</t>
+          <t>323218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124832</t>
+          <t>125388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68229</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>97637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118833</t>
+          <t>118258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210766</t>
+          <t>210708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>325466</t>
+          <t>288609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>776096</t>
+          <t>778000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>632920</t>
+          <t>634871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>682113</t>
+          <t>684307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>849489</t>
+          <t>858622</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1442806</t>
+          <t>1444983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300759</t>
+          <t>300572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>808562</t>
+          <t>853208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>194312</t>
+          <t>193486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241071</t>
+          <t>238621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>517003</t>
+          <t>512795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1179372</t>
+          <t>1176276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>120890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170324</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82012</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209514</t>
+          <t>204688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>200486</t>
+          <t>205993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>352923</t>
+          <t>357377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>425788</t>
+          <t>427576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>484592</t>
+          <t>485347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>609499</t>
+          <t>609913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>803996</t>
+          <t>823935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1059263</t>
+          <t>1059304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1306569</t>
+          <t>1308962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84797</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124870</t>
+          <t>124419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46467</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123089</t>
+          <t>123808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128956</t>
+          <t>124836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233288</t>
+          <t>233660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83362</t>
+          <t>83263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127395</t>
+          <t>128540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104808</t>
+          <t>104126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355342</t>
+          <t>339195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>204809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>529689</t>
+          <t>482843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485663</t>
+          <t>486471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550126</t>
+          <t>550261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>455200</t>
+          <t>456508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>636503</t>
+          <t>635668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>978608</t>
+          <t>977672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1166912</t>
+          <t>1165266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>274114</t>
+          <t>276010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>337498</t>
+          <t>337635</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>269325</t>
+          <t>266209</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>371448</t>
+          <t>371590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>558735</t>
+          <t>558240</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>687072</t>
+          <t>686494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>410684</t>
+          <t>411854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>360218</t>
+          <t>358228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>665407</t>
+          <t>630368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>697379</t>
+          <t>697165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1047950</t>
+          <t>1008827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1534447</t>
+          <t>1564751</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2234853</t>
+          <t>2234341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2344843</t>
+          <t>2339506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2697045</t>
+          <t>2684967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4006382</t>
+          <t>4000677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4768861</t>
+          <t>4785092</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>840456</t>
+          <t>836418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1655221</t>
+          <t>1618815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>636803</t>
+          <t>629149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>859315</t>
+          <t>861343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1605976</t>
+          <t>1589681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2581119</t>
+          <t>2486275</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40025</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75898</t>
+          <t>75134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452609</t>
+          <t>452703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501925</t>
+          <t>504791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448131</t>
+          <t>450308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>498821</t>
+          <t>498743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>916399</t>
+          <t>914496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>988973</t>
+          <t>986418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173217</t>
+          <t>173947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221445</t>
+          <t>222455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168809</t>
+          <t>169863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217224</t>
+          <t>216827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>355411</t>
+          <t>356814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>425357</t>
+          <t>423568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>639185</t>
+          <t>637021</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>701467</t>
+          <t>701652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>666146</t>
+          <t>669669</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>728452</t>
+          <t>733027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1326679</t>
+          <t>1326375</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1416534</t>
+          <t>1416791</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>289341</t>
+          <t>288088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>349678</t>
+          <t>350236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>272245</t>
+          <t>271146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333427</t>
+          <t>330476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>574939</t>
+          <t>575927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>660940</t>
+          <t>658735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57854</t>
+          <t>59311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121333</t>
+          <t>119168</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>475605</t>
+          <t>476834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>532016</t>
+          <t>530530</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>533370</t>
+          <t>531069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>584425</t>
+          <t>586713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1029098</t>
+          <t>1027453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105108</t>
+          <t>1103062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169126</t>
+          <t>172995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222923</t>
+          <t>222603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153548</t>
+          <t>150890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200012</t>
+          <t>202123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336216</t>
+          <t>338167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406211</t>
+          <t>408101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>102932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472018</t>
+          <t>473548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532639</t>
+          <t>535214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529058</t>
+          <t>528093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>593701</t>
+          <t>595704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1022097</t>
+          <t>1016643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114923</t>
+          <t>1106992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>388944</t>
+          <t>385767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>450523</t>
+          <t>447167</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>404530</t>
+          <t>401472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>469477</t>
+          <t>469258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>804511</t>
+          <t>808203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>895496</t>
+          <t>898567</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118571</t>
+          <t>117106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167116</t>
+          <t>167635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136385</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187873</t>
+          <t>189018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267675</t>
+          <t>269652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337458</t>
+          <t>339063</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2100521</t>
+          <t>2096764</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2219218</t>
+          <t>2214659</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2238353</t>
+          <t>2238515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2357039</t>
+          <t>2352332</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4364789</t>
+          <t>4362800</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4534816</t>
+          <t>4534267</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1072620</t>
+          <t>1076408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1184169</t>
+          <t>1189026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1045111</t>
+          <t>1047579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1160957</t>
+          <t>1153325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2142505</t>
+          <t>2148760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2305997</t>
+          <t>2308780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145631</t>
+          <t>146816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96742</t>
+          <t>94893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134848</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211457</t>
+          <t>214654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267855</t>
+          <t>268621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>338898</t>
+          <t>338180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390805</t>
+          <t>390116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>345221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398056</t>
+          <t>398793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>700996</t>
+          <t>702107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772927</t>
+          <t>773533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161347</t>
+          <t>162232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>208867</t>
+          <t>208594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161435</t>
+          <t>163306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205810</t>
+          <t>208153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>337334</t>
+          <t>333935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>403957</t>
+          <t>403425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128412</t>
+          <t>128652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176575</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121947</t>
+          <t>122457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167439</t>
+          <t>167179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263652</t>
+          <t>262222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329692</t>
+          <t>327453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>545889</t>
+          <t>549998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>612094</t>
+          <t>609025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>556906</t>
+          <t>552502</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>626611</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1119622</t>
+          <t>1118860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1216867</t>
+          <t>1212610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>262351</t>
+          <t>263285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323775</t>
+          <t>321013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>280837</t>
+          <t>282350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>340356</t>
+          <t>341576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>560203</t>
+          <t>560706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>648375</t>
+          <t>646918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134562</t>
+          <t>132994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>181188</t>
+          <t>179289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132408</t>
+          <t>130280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179656</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276711</t>
+          <t>276585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>347597</t>
+          <t>342044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>296195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>351872</t>
+          <t>352889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>293719</t>
+          <t>293548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>350233</t>
+          <t>350294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608545</t>
+          <t>609503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>692895</t>
+          <t>691416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249675</t>
+          <t>249013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305184</t>
+          <t>304991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284533</t>
+          <t>282917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>341422</t>
+          <t>339287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>546804</t>
+          <t>549843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>628439</t>
+          <t>629784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82254</t>
+          <t>80896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122508</t>
+          <t>121613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123730</t>
+          <t>125338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178325</t>
+          <t>174553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>235450</t>
+          <t>234654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496965</t>
+          <t>495807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556478</t>
+          <t>560474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527398</t>
+          <t>533465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>597560</t>
+          <t>598394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1043821</t>
+          <t>1044253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1137982</t>
+          <t>1135988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>279364</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>339902</t>
+          <t>338841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>343681</t>
+          <t>343210</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>411128</t>
+          <t>407833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>638202</t>
+          <t>645442</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>729393</t>
+          <t>731605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>492038</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>577072</t>
+          <t>577793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>476803</t>
+          <t>472346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>562513</t>
+          <t>560787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>986040</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1118529</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1738456</t>
+          <t>1739624</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1856736</t>
+          <t>1855218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1781384</t>
+          <t>1785061</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1905651</t>
+          <t>1908236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3560251</t>
+          <t>3556327</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3726090</t>
+          <t>3722595</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1013439</t>
+          <t>1012908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1120759</t>
+          <t>1122201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1124295</t>
+          <t>1128057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1239099</t>
+          <t>1244241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2170944</t>
+          <t>2164920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2326782</t>
+          <t>2328753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34177</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>476372</t>
+          <t>514474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448394</t>
+          <t>488119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499366</t>
+          <t>538023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>540264</t>
+          <t>534808</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>516730</t>
+          <t>511683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>578071</t>
+          <t>552629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1016635</t>
+          <t>1049282</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>976946</t>
+          <t>1017335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1056738</t>
+          <t>1081077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134890</t>
+          <t>142840</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112619</t>
+          <t>121338</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165460</t>
+          <t>168104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149254</t>
+          <t>156928</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119550</t>
+          <t>136709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170174</t>
+          <t>176844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>284144</t>
+          <t>299769</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249660</t>
+          <t>271198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323218</t>
+          <t>332106</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90507</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>86281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125388</t>
+          <t>133521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>97262</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>82146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97637</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>173280</t>
+          <t>206177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>179776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210708</t>
+          <t>235189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>607652</t>
+          <t>676812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>288609</t>
+          <t>640864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>778000</t>
+          <t>714312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>660404</t>
+          <t>742138</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>634871</t>
+          <t>714309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>684307</t>
+          <t>768882</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>1418950</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>858622</t>
+          <t>1378610</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1444983</t>
+          <t>1463835</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>494704</t>
+          <t>263191</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300572</t>
+          <t>231106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>853208</t>
+          <t>299284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>215475</t>
+          <t>232074</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193486</t>
+          <t>209363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238621</t>
+          <t>257864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>710179</t>
+          <t>495264</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512795</t>
+          <t>454435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1176276</t>
+          <t>534193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6546,17 +6546,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120890</t>
+          <t>149711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172989</t>
+          <t>204907</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>194190</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>171483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>204688</t>
+          <t>217272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>296526</t>
+          <t>369683</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>205993</t>
+          <t>337087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>357377</t>
+          <t>406646</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>457039</t>
+          <t>501185</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>427576</t>
+          <t>468929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>485347</t>
+          <t>531821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>690650</t>
+          <t>511530</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>609913</t>
+          <t>485289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>823935</t>
+          <t>535304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1147689</t>
+          <t>1012715</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1059304</t>
+          <t>968811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1308962</t>
+          <t>1051454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>103698</t>
+          <t>126395</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>105916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124419</t>
+          <t>151878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90133</t>
+          <t>106539</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123808</t>
+          <t>126310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>193831</t>
+          <t>232935</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124836</t>
+          <t>204922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233660</t>
+          <t>263592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7002,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>117561</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83263</t>
+          <t>97089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128540</t>
+          <t>143919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>172658</t>
+          <t>122233</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104126</t>
+          <t>105550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339195</t>
+          <t>143309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>276519</t>
+          <t>239793</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204809</t>
+          <t>213233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482843</t>
+          <t>274110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>517857</t>
+          <t>559963</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>486471</t>
+          <t>527492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550261</t>
+          <t>595026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>586344</t>
+          <t>634723</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456508</t>
+          <t>603587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635668</t>
+          <t>663787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1104201</t>
+          <t>1194686</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977672</t>
+          <t>1149346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1165266</t>
+          <t>1240155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>305113</t>
+          <t>312539</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>276010</t>
+          <t>282796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>337635</t>
+          <t>345321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>335930</t>
+          <t>362085</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>266209</t>
+          <t>333331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>371590</t>
+          <t>392044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>641044</t>
+          <t>674624</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>558240</t>
+          <t>636368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>686494</t>
+          <t>718511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7458,17 +7458,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276593</t>
+          <t>392665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>411854</t>
+          <t>481883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>358228</t>
+          <t>418692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>630368</t>
+          <t>492341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>697165</t>
+          <t>832728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1008827</t>
+          <t>947016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1564751</t>
+          <t>2188561</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2234341</t>
+          <t>2316488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2339506</t>
+          <t>2372164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2684967</t>
+          <t>2475473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4000677</t>
+          <t>4579598</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4785092</t>
+          <t>4749899</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1038405</t>
+          <t>844965</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>836418</t>
+          <t>790926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1618815</t>
+          <t>905445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>790793</t>
+          <t>857626</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629149</t>
+          <t>813957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>861343</t>
+          <t>901540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1829198</t>
+          <t>1702592</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1589681</t>
+          <t>1631223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2486275</t>
+          <t>1779453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -7914,17 +7914,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7949,17 +7949,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
